--- a/tests/fixtures/autofilter_file/autofilter.xlsx
+++ b/tests/fixtures/autofilter_file/autofilter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\autofilter_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3403A18D-04E3-49A4-B804-AA9BF1A1D687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E67781EB-EF02-40AE-B14A-F7750D53AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="7200" windowHeight="4425" firstSheet="33" activeTab="33" xr2:uid="{3B1D173C-4E85-48F9-BFB7-B2018B4FECC9}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="7200" windowHeight="4425" firstSheet="40" activeTab="40" xr2:uid="{241C9F2A-CEC5-4073-865A-2250D80691C7}"/>
   </bookViews>
   <sheets>
     <sheet name="arrows" sheetId="1" r:id="rId1"/>
@@ -47,6 +47,13 @@
     <sheet name="and_plain" sheetId="32" r:id="rId32"/>
     <sheet name="or_blank" sheetId="33" r:id="rId33"/>
     <sheet name="decimal_greater" sheetId="34" r:id="rId34"/>
+    <sheet name="grown_below" sheetId="35" r:id="rId35"/>
+    <sheet name="grown_reapplied" sheetId="36" r:id="rId36"/>
+    <sheet name="sub_range" sheetId="37" r:id="rId37"/>
+    <sheet name="sub_range_arrows" sheetId="38" r:id="rId38"/>
+    <sheet name="sub_range_then_field" sheetId="39" r:id="rId39"/>
+    <sheet name="sub_range_refiltered" sheetId="40" r:id="rId40"/>
+    <sheet name="sub_range_mid" sheetId="41" r:id="rId41"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">above_average!$F$1:$F$9</definedName>
@@ -64,6 +71,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">equals!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">escaped!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">greater!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">grown_below!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">grown_reapplied!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">hidden_button!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">non_blanks!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">not_equal!$A$1:$D$13</definedName>
@@ -73,6 +82,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">or_blank!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">or_custom!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">shown_all!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">sub_range!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">sub_range_arrows!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">sub_range_mid!$A$3:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">sub_range_refiltered!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">sub_range_then_field!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">text_greater!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">time_after!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">top_items!$F$1:$F$9</definedName>
@@ -108,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -165,6 +179,9 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>pear</t>
   </si>
 </sst>
 </file>
@@ -539,7 +556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A51570-A06E-424F-89C5-9CA7D618830D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8273A2-AB93-44DD-8F31-0C9BBD186591}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -694,13 +711,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{C9A51570-A06E-424F-89C5-9CA7D618830D}"/>
+  <autoFilter ref="A1:D13" xr:uid="{1F8273A2-AB93-44DD-8F31-0C9BBD186591}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4524D0-3075-4CDE-9A13-D1B4F003FB7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A46F67-E2F7-4359-84ED-9AC3C67E0416}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -856,7 +873,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{3A4524D0-3075-4CDE-9A13-D1B4F003FB7D}">
+  <autoFilter ref="A1:D13" xr:uid="{D4A46F67-E2F7-4359-84ED-9AC3C67E0416}">
     <filterColumn colId="3">
       <filters blank="1">
         <filter val="x"/>
@@ -869,7 +886,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CA276B-24AD-4B20-9F0E-75E4E198744A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C54F980-63B3-4E18-ABFA-085CB5AB5697}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1052,7 +1069,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F9" xr:uid="{B7CA276B-24AD-4B20-9F0E-75E4E198744A}">
+  <autoFilter ref="F1:F9" xr:uid="{7C54F980-63B3-4E18-ABFA-085CB5AB5697}">
     <filterColumn colId="0">
       <top10 val="3" filterVal="7"/>
     </filterColumn>
@@ -1062,7 +1079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C06936-7126-4AD2-A064-2673A2039B47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92196363-3057-4F63-A615-795E1A63070F}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1245,7 +1262,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F9" xr:uid="{77C06936-7126-4AD2-A064-2673A2039B47}">
+  <autoFilter ref="F1:F9" xr:uid="{92196363-3057-4F63-A615-795E1A63070F}">
     <filterColumn colId="0">
       <top10 percent="1" val="25" filterVal="9"/>
     </filterColumn>
@@ -1255,7 +1272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156C6388-2908-4AB8-9D6C-C806F27389DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864B91F7-95AD-436E-931F-1303B797C7CA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1438,7 +1455,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F9" xr:uid="{156C6388-2908-4AB8-9D6C-C806F27389DF}">
+  <autoFilter ref="F1:F9" xr:uid="{864B91F7-95AD-436E-931F-1303B797C7CA}">
     <filterColumn colId="0">
       <top10 top="0" val="2" filterVal="1"/>
     </filterColumn>
@@ -1448,7 +1465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2EFDF9-9024-4845-B537-8CD47EA687F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F53EBF-E27F-4DB6-BAE5-0A01FBCA2F23}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1631,7 +1648,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F9" xr:uid="{EE2EFDF9-9024-4845-B537-8CD47EA687F9}">
+  <autoFilter ref="F1:F9" xr:uid="{D3F53EBF-E27F-4DB6-BAE5-0A01FBCA2F23}">
     <filterColumn colId="0">
       <dynamicFilter type="aboveAverage" val="5.0625"/>
     </filterColumn>
@@ -1641,7 +1658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5764EC08-C1F1-4F58-8868-A6DEA7DE12F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF8BA4-4109-4355-A340-2B20EFCEED64}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1824,7 +1841,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F9" xr:uid="{5764EC08-C1F1-4F58-8868-A6DEA7DE12F3}">
+  <autoFilter ref="F1:F9" xr:uid="{D3DF8BA4-4109-4355-A340-2B20EFCEED64}">
     <filterColumn colId="0">
       <dynamicFilter type="belowAverage" val="5.0625"/>
     </filterColumn>
@@ -1834,7 +1851,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3995192-645D-480A-884F-8F4F9ADF6042}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2C2465-C5CC-4AAD-84F4-79B75D06CF31}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1990,7 +2007,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{D3995192-645D-480A-884F-8F4F9ADF6042}">
+  <autoFilter ref="A1:D13" xr:uid="{7C2C2465-C5CC-4AAD-84F4-79B75D06CF31}">
     <filterColumn colId="3">
       <filters blank="1"/>
     </filterColumn>
@@ -2000,7 +2017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9EB1FC-4427-4139-9217-6FC2738653AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98113558-7BFB-494C-A5E5-5DC1A6CD4C45}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2156,7 +2173,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{2C9EB1FC-4427-4139-9217-6FC2738653AA}">
+  <autoFilter ref="A1:D13" xr:uid="{98113558-7BFB-494C-A5E5-5DC1A6CD4C45}">
     <filterColumn colId="3">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -2168,7 +2185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1358E76B-04E9-40A3-8973-BAEA6F426214}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7602FCD7-678C-4D7E-AC90-CB40BB37F3A3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2324,7 +2341,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{1358E76B-04E9-40A3-8973-BAEA6F426214}">
+  <autoFilter ref="A1:D13" xr:uid="{7602FCD7-678C-4D7E-AC90-CB40BB37F3A3}">
     <filterColumn colId="0">
       <filters>
         <filter val="cherry"/>
@@ -2341,7 +2358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E7C25-41D5-45D7-9856-176162A8BEB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B68B0F-0A8D-4D7A-A6CF-84709223C47F}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2497,7 +2514,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{0E4E7C25-41D5-45D7-9856-176162A8BEB7}">
+  <autoFilter ref="A1:D13" xr:uid="{A6B68B0F-0A8D-4D7A-A6CF-84709223C47F}">
     <filterColumn colId="2">
       <customFilters>
         <customFilter operator="greaterThan" val="43845"/>
@@ -2509,7 +2526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A37F3E0-96A3-417E-9BAD-7AC364F1C945}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5336CF8-AB64-44DF-9F4E-4145D43CD10D}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2665,7 +2682,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{8A37F3E0-96A3-417E-9BAD-7AC364F1C945}">
+  <autoFilter ref="A1:D13" xr:uid="{D5336CF8-AB64-44DF-9F4E-4145D43CD10D}">
     <filterColumn colId="0">
       <filters>
         <filter val="apple"/>
@@ -2677,7 +2694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E111D5E-1517-405E-9CD2-B68F675B7C0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260D2518-CDA2-4CB9-AA50-E09AF369CD78}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2833,7 +2850,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{9E111D5E-1517-405E-9CD2-B68F675B7C0E}">
+  <autoFilter ref="A1:D13" xr:uid="{260D2518-CDA2-4CB9-AA50-E09AF369CD78}">
     <filterColumn colId="2">
       <filters>
         <filter val="1/15/2020"/>
@@ -2845,7 +2862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0000351-C922-4CDB-891F-B6813B4A888D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD88CBF-32FC-4F4F-B7C0-1880DD5E5B1E}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3001,7 +3018,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{C0000351-C922-4CDB-891F-B6813B4A888D}">
+  <autoFilter ref="A1:D13" xr:uid="{BAD88CBF-32FC-4F4F-B7C0-1880DD5E5B1E}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="greaterThan" val="b"/>
@@ -3013,7 +3030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D292821-4664-4B44-BAD4-5AD4824B86DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1133B2-0AD0-4F01-934F-C8B7DF7002F4}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3169,7 +3186,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{4D292821-4664-4B44-BAD4-5AD4824B86DB}">
+  <autoFilter ref="A1:D13" xr:uid="{4A1133B2-0AD0-4F01-934F-C8B7DF7002F4}">
     <filterColumn colId="1">
       <filters>
         <filter val="1"/>
@@ -3181,7 +3198,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27F3649-C204-4432-B293-9D1CC1589F68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED865C15-7008-4FC1-BB4A-680361344201}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3337,7 +3354,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{C27F3649-C204-4432-B293-9D1CC1589F68}">
+  <autoFilter ref="A1:D13" xr:uid="{ED865C15-7008-4FC1-BB4A-680361344201}">
     <filterColumn colId="1">
       <filters>
         <filter val="1.00"/>
@@ -3349,7 +3366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB68287-B3A8-4DD0-81BD-D14DA00E86C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C3575D-076B-425D-9216-EA649F65E165}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3505,7 +3522,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{6FB68287-B3A8-4DD0-81BD-D14DA00E86C7}">
+  <autoFilter ref="A1:D13" xr:uid="{D4C3575D-076B-425D-9216-EA649F65E165}">
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="notEqual" val="2"/>
@@ -3517,7 +3534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124C1787-BE44-4648-BF48-701E80CCBFF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5F5551-D4BB-4829-8EB8-88D3B57BD686}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3673,7 +3690,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{124C1787-BE44-4648-BF48-701E80CCBFF7}">
+  <autoFilter ref="A1:D13" xr:uid="{9A5F5551-D4BB-4829-8EB8-88D3B57BD686}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter val="*"/>
@@ -3685,7 +3702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BC2065-98D9-4A91-98D7-07A1055F6D8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEA936B-8B66-4724-BDB3-3C385B5B86A3}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3840,13 +3857,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{11BC2065-98D9-4A91-98D7-07A1055F6D8B}"/>
+  <autoFilter ref="A1:D13" xr:uid="{1AEA936B-8B66-4724-BDB3-3C385B5B86A3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C26A5D86-2AC3-4F49-9866-E301829FB860}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEA1FB8-E175-4A16-8270-CA44F2B38237}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4006,7 +4023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD315464-E03B-43CD-AA60-288B49A879C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862CC066-280F-405C-B5C5-01FAB45B3D96}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4162,7 +4179,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{CD315464-E03B-43CD-AA60-288B49A879C9}">
+  <autoFilter ref="A1:D13" xr:uid="{862CC066-280F-405C-B5C5-01FAB45B3D96}">
     <filterColumn colId="0">
       <filters>
         <filter val="b*"/>
@@ -4174,7 +4191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52185604-3E74-485B-AA8F-D1071AE0A23A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6ED827-0B12-468A-BE72-4ACFF1F5A112}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4330,7 +4347,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{52185604-3E74-485B-AA8F-D1071AE0A23A}">
+  <autoFilter ref="A1:D13" xr:uid="{AA6ED827-0B12-468A-BE72-4ACFF1F5A112}">
     <filterColumn colId="2">
       <customFilters>
         <customFilter operator="greaterThan" val="43845.208333333336"/>
@@ -4342,7 +4359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC0E91A-CB4F-4BCE-BF82-B21DB14C4D52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8828804C-B758-4280-858E-A03E6897E9CB}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4498,7 +4515,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{7AC0E91A-CB4F-4BCE-BF82-B21DB14C4D52}">
+  <autoFilter ref="A1:D13" xr:uid="{8828804C-B758-4280-858E-A03E6897E9CB}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter val="a*"/>
@@ -4510,7 +4527,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{073C9257-B8B0-4AA6-BCDD-836438A9AC24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C96D3E4-5FF0-40F9-A8D4-A1D9AEFF9285}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4666,7 +4683,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{073C9257-B8B0-4AA6-BCDD-836438A9AC24}">
+  <autoFilter ref="A1:D13" xr:uid="{4C96D3E4-5FF0-40F9-A8D4-A1D9AEFF9285}">
     <filterColumn colId="0" hiddenButton="1">
       <filters>
         <filter val="apple"/>
@@ -4678,7 +4695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00FE871-BB74-4DD9-A14A-FED9FEF0371C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE5E139-7348-4697-8779-FB6837002AF4}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4834,7 +4851,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{B00FE871-BB74-4DD9-A14A-FED9FEF0371C}">
+  <autoFilter ref="A1:D13" xr:uid="{2FE5E139-7348-4697-8779-FB6837002AF4}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter val="a*"/>
@@ -4847,7 +4864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5606F3B-7613-4F41-8935-CC9A3407654A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FBC68E-9E29-4374-9358-CD158CF20625}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5003,7 +5020,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{D5606F3B-7613-4F41-8935-CC9A3407654A}">
+  <autoFilter ref="A1:D13" xr:uid="{C2FBC68E-9E29-4374-9358-CD158CF20625}">
     <filterColumn colId="0">
       <customFilters and="1">
         <customFilter val="apple"/>
@@ -5016,7 +5033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C164DF1F-5FB8-40C0-8C75-46777733A2CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A52D810B-AD05-48BD-A1A6-4E8056D22B11}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5172,7 +5189,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{C164DF1F-5FB8-40C0-8C75-46777733A2CA}">
+  <autoFilter ref="A1:D13" xr:uid="{A52D810B-AD05-48BD-A1A6-4E8056D22B11}">
     <filterColumn colId="3">
       <filters blank="1">
         <filter val="x"/>
@@ -5184,7 +5201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7ACE775-837C-4107-B431-117CAFEAEF8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F1726D6-8E40-4106-AEB4-2380AEE3E2B1}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5340,7 +5357,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{F7ACE775-837C-4107-B431-117CAFEAEF8E}">
+  <autoFilter ref="A1:D13" xr:uid="{5F1726D6-8E40-4106-AEB4-2380AEE3E2B1}">
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="greaterThan" val="2.5"/>
@@ -5351,8 +5368,354 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22546CA-18DA-4890-B8F5-F7E7B4154E56}">
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300CC880-6175-4A36-A564-4D7827E7BA8F}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13" xr:uid="{300CC880-6175-4A36-A564-4D7827E7BA8F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="apple"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C70AEBB-566A-4DA7-A1AD-F1D671DEC8D0}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D14" xr:uid="{0C70AEBB-566A-4DA7-A1AD-F1D671DEC8D0}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="apple"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F04EA06-DFB9-48A3-8571-0667B2737C61}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5371,6 +5734,503 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13" xr:uid="{5F04EA06-DFB9-48A3-8571-0667B2737C61}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="apple"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8411F03-3B0F-4D50-84E8-5F8028797BE6}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D5" xr:uid="{D8411F03-3B0F-4D50-84E8-5F8028797BE6}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C95D3F-7628-4897-A5A2-BF3C37411EFD}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13" xr:uid="{01C95D3F-7628-4897-A5A2-BF3C37411EFD}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="apple"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F2ED72B-6114-4516-A01A-5C0180F46DA1}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
@@ -5508,7 +6368,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{A22546CA-18DA-4890-B8F5-F7E7B4154E56}">
+  <autoFilter ref="A1:D13" xr:uid="{7F2ED72B-6114-4516-A01A-5C0180F46DA1}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val="apple"/>
@@ -5519,8 +6379,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AABF81-5A00-44A0-9F8C-EE918AF0ACAD}">
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142D4112-2583-49BD-856E-F2312D682EC8}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5553,6 +6413,347 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13" xr:uid="{142D4112-2583-49BD-856E-F2312D682EC8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="apple"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="greaterThan" val="1"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98061C5A-2175-4BC8-8BB3-F93EB0A729CC}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>43862</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43845.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>43845</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D13" xr:uid="{98061C5A-2175-4BC8-8BB3-F93EB0A729CC}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="apple"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEB29FC-C2C7-4C81-848B-39EB53BCEE1E}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>43831</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
@@ -5676,7 +6877,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{F2AABF81-5A00-44A0-9F8C-EE918AF0ACAD}">
+  <autoFilter ref="A1:D13" xr:uid="{1AEB29FC-C2C7-4C81-848B-39EB53BCEE1E}">
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="greaterThan" val="2"/>
@@ -5688,7 +6889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F3327C-8718-4E1D-8B5C-4E943D601E74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6104D5ED-B7C0-4311-B95E-492A65AE775D}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5844,7 +7045,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{D7F3327C-8718-4E1D-8B5C-4E943D601E74}">
+  <autoFilter ref="A1:D13" xr:uid="{6104D5ED-B7C0-4311-B95E-492A65AE775D}">
     <filterColumn colId="1">
       <customFilters and="1">
         <customFilter operator="greaterThanOrEqual" val="1"/>
@@ -5857,7 +7058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14AB25C2-2422-4ECD-A721-689DE1FCDDE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0BA0C41-4151-4D59-A362-37743036C4AC}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6013,7 +7214,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{14AB25C2-2422-4ECD-A721-689DE1FCDDE4}">
+  <autoFilter ref="A1:D13" xr:uid="{C0BA0C41-4151-4D59-A362-37743036C4AC}">
     <filterColumn colId="0">
       <filters>
         <filter val="apple"/>
@@ -6026,7 +7227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC42FC9B-166E-42EE-A738-E1FBE69F3EB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6699311-6484-426A-A54C-80649EF97685}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6182,7 +7383,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{AC42FC9B-166E-42EE-A738-E1FBE69F3EB8}">
+  <autoFilter ref="A1:D13" xr:uid="{C6699311-6484-426A-A54C-80649EF97685}">
     <filterColumn colId="0">
       <filters>
         <filter val="apple"/>
@@ -6196,7 +7397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9A6658-81BA-4A1C-9DE5-88CBD31552B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FDDA229-2F57-43BB-AA2D-147DDCE52B8A}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6352,7 +7553,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13" xr:uid="{DB9A6658-81BA-4A1C-9DE5-88CBD31552B4}">
+  <autoFilter ref="A1:D13" xr:uid="{6FDDA229-2F57-43BB-AA2D-147DDCE52B8A}">
     <filterColumn colId="0">
       <filters>
         <filter val="apple"/>

--- a/tests/fixtures/autofilter_file/autofilter.xlsx
+++ b/tests/fixtures/autofilter_file/autofilter.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\autofilter_file\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{E67781EB-EF02-40AE-B14A-F7750D53AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="7200" windowHeight="4425" firstSheet="40" activeTab="40" xr2:uid="{241C9F2A-CEC5-4073-865A-2250D80691C7}"/>
